--- a/data/trans_orig/IP22C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22C-Provincia-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27613</t>
+          <t>27439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>31048</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38882</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28861</t>
+          <t>28721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22462</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27256</t>
+          <t>27257</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>52304</t>
+          <t>52237</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57792</t>
+          <t>57798</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -3695,82 +3695,82 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>4907</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>17,58%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>10,59%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
           <t>664</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>5458</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>3060</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24647</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>42928</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>114183</t>
+          <t>114541</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>122533</t>
+          <t>122677</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>135007</t>
+          <t>134622</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>145086</t>
+          <t>144948</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>252111</t>
+          <t>252863</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>265067</t>
+          <t>265583</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25533</t>
+          <t>25570</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>29578</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36335</t>
+          <t>36820</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57215</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65070</t>
+          <t>64852</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17810</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34097</t>
+          <t>34109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40312</t>
+          <t>40305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>23626</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37272</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41449</t>
+          <t>41452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>25796</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>31322</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36483</t>
+          <t>36467</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>27029</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37727</t>
+          <t>38037</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>67108</t>
+          <t>66613</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15014</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>21563</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>139332</t>
+          <t>139443</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>149934</t>
+          <t>149415</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>180717</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>192555</t>
+          <t>192807</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>324109</t>
+          <t>323174</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>340040</t>
+          <t>340153</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20748</t>
+          <t>20745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>36275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41619</t>
+          <t>41483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>541</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25320</t>
+          <t>25313</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22303</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>49449</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54223</t>
+          <t>54225</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33133</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,49%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>58,26%</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23901</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31441</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>99191</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>109309</t>
+          <t>109689</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>90401</t>
+          <t>90483</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>101999</t>
+          <t>102156</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>193632</t>
+          <t>193585</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>209572</t>
+          <t>208802</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>24999</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35348</t>
+          <t>35037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>41050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>477</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27468</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>23020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -16181,7 +16181,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18672</t>
+          <t>19120</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31110</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53847</t>
+          <t>53424</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60763</t>
+          <t>60837</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16805,7 +16805,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>361</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>357</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -17406,7 +17406,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17421,7 +17421,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>83094</t>
+          <t>82879</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>92466</t>
+          <t>92389</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>95364</t>
+          <t>94476</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>106010</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>182002</t>
+          <t>181580</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>196902</t>
+          <t>196510</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
